--- a/Thoikhoabieu.xlsx
+++ b/Thoikhoabieu.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="14">
   <si>
     <t>Thứ 2</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>TH hóa sinh</t>
+  </si>
+  <si>
+    <t>TH MÔ PHÔI</t>
   </si>
 </sst>
 </file>
@@ -1210,8 +1213,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="7"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="12.5555555555556" customWidth="1"/>
     <col min="2" max="2" width="16.2222222222222" customWidth="1"/>
@@ -1279,8 +1282,69 @@
       <c r="B3" t="s">
         <v>12</v>
       </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
       <c r="E3" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1" spans="1:8">
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:8">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1" spans="1:8">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
